--- a/data/EN/games_config/toxic_games_5_USA.xlsx
+++ b/data/EN/games_config/toxic_games_5_USA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\!Master\Tesis\3 Codigo\Cards_Against_AI\data\EN\games_config\games\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vfionda/Library/CloudStorage/GoogleDrive-valeria.fionda@unical.it/My Drive/didattica/Tesi/2025/Artigas Herold/Cards_Against_AI/data/EN/games_config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE90771E-6C4D-45CA-8F9E-F1DBA775D23E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41B36B83-87F9-0B40-8A58-E6BEA4E27AD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="23260" windowHeight="12460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet_1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="477">
   <si>
     <t>black_id</t>
   </si>
@@ -1419,9 +1419,6 @@
   </si>
   <si>
     <t>W204</t>
-  </si>
-  <si>
-    <t>w213</t>
   </si>
   <si>
     <t>W123</t>
@@ -1485,6 +1482,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1836,19 +1834,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J229"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="11.6640625" customWidth="1"/>
     <col min="4" max="4" width="10.33203125" customWidth="1"/>
-    <col min="5" max="5" width="11.77734375" customWidth="1"/>
-    <col min="6" max="6" width="10.5546875" customWidth="1"/>
-    <col min="7" max="7" width="10.88671875" customWidth="1"/>
-    <col min="8" max="8" width="11.109375" customWidth="1"/>
-    <col min="9" max="9" width="11.21875" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" customWidth="1"/>
+    <col min="8" max="9" width="11.1640625" customWidth="1"/>
+    <col min="10" max="10" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>93</v>
       </c>
@@ -1874,7 +1871,7 @@
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>94</v>
       </c>
@@ -1897,7 +1894,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>94</v>
       </c>
@@ -1920,7 +1917,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>94</v>
       </c>
@@ -1943,7 +1940,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>94</v>
       </c>
@@ -1966,7 +1963,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>94</v>
       </c>
@@ -1989,7 +1986,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>94</v>
       </c>
@@ -2012,7 +2009,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>94</v>
       </c>
@@ -2035,7 +2032,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>94</v>
       </c>
@@ -2058,7 +2055,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>94</v>
       </c>
@@ -2081,7 +2078,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>94</v>
       </c>
@@ -2104,7 +2101,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>94</v>
       </c>
@@ -2127,7 +2124,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>94</v>
       </c>
@@ -2150,7 +2147,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>94</v>
       </c>
@@ -2173,7 +2170,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>94</v>
       </c>
@@ -2196,7 +2193,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>94</v>
       </c>
@@ -2219,7 +2216,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>94</v>
       </c>
@@ -2242,7 +2239,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>94</v>
       </c>
@@ -2265,7 +2262,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>94</v>
       </c>
@@ -2288,7 +2285,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>94</v>
       </c>
@@ -2311,7 +2308,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>94</v>
       </c>
@@ -2334,7 +2331,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>94</v>
       </c>
@@ -2357,7 +2354,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>94</v>
       </c>
@@ -2380,7 +2377,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>94</v>
       </c>
@@ -2403,7 +2400,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>94</v>
       </c>
@@ -2426,7 +2423,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>94</v>
       </c>
@@ -2449,7 +2446,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>94</v>
       </c>
@@ -2472,7 +2469,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>94</v>
       </c>
@@ -2495,7 +2492,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>94</v>
       </c>
@@ -2518,7 +2515,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>94</v>
       </c>
@@ -2541,7 +2538,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>94</v>
       </c>
@@ -2564,7 +2561,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>94</v>
       </c>
@@ -2587,7 +2584,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>94</v>
       </c>
@@ -2610,7 +2607,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>94</v>
       </c>
@@ -2633,7 +2630,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>94</v>
       </c>
@@ -2656,7 +2653,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>94</v>
       </c>
@@ -2679,7 +2676,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>94</v>
       </c>
@@ -2702,7 +2699,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>94</v>
       </c>
@@ -2725,7 +2722,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>94</v>
       </c>
@@ -2748,7 +2745,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>94</v>
       </c>
@@ -2771,7 +2768,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>94</v>
       </c>
@@ -2794,7 +2791,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>94</v>
       </c>
@@ -2817,7 +2814,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>94</v>
       </c>
@@ -2840,7 +2837,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>94</v>
       </c>
@@ -2863,7 +2860,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>94</v>
       </c>
@@ -2886,7 +2883,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>94</v>
       </c>
@@ -2909,7 +2906,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>94</v>
       </c>
@@ -2932,7 +2929,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>94</v>
       </c>
@@ -2955,7 +2952,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>94</v>
       </c>
@@ -2978,7 +2975,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>94</v>
       </c>
@@ -3001,7 +2998,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>94</v>
       </c>
@@ -3024,7 +3021,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>94</v>
       </c>
@@ -3047,7 +3044,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>94</v>
       </c>
@@ -3070,7 +3067,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>94</v>
       </c>
@@ -3093,7 +3090,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>94</v>
       </c>
@@ -3116,7 +3113,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>94</v>
       </c>
@@ -3139,7 +3136,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>94</v>
       </c>
@@ -3162,7 +3159,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>94</v>
       </c>
@@ -3185,7 +3182,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>94</v>
       </c>
@@ -3208,7 +3205,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>94</v>
       </c>
@@ -3231,7 +3228,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>94</v>
       </c>
@@ -3254,7 +3251,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>94</v>
       </c>
@@ -3277,7 +3274,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>94</v>
       </c>
@@ -3300,7 +3297,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>94</v>
       </c>
@@ -3323,7 +3320,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>94</v>
       </c>
@@ -3346,7 +3343,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>94</v>
       </c>
@@ -3369,7 +3366,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>94</v>
       </c>
@@ -3392,7 +3389,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>94</v>
       </c>
@@ -3406,7 +3403,7 @@
         <v>330</v>
       </c>
       <c r="E68" t="s">
-        <v>462</v>
+        <v>427</v>
       </c>
       <c r="F68" t="s">
         <v>403</v>
@@ -3415,7 +3412,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>94</v>
       </c>
@@ -3438,7 +3435,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>94</v>
       </c>
@@ -3461,7 +3458,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>94</v>
       </c>
@@ -3478,13 +3475,13 @@
         <v>381</v>
       </c>
       <c r="F71" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="G71" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>94</v>
       </c>
@@ -3498,7 +3495,7 @@
         <v>303</v>
       </c>
       <c r="E72" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F72" t="s">
         <v>426</v>
@@ -3507,7 +3504,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>94</v>
       </c>
@@ -3530,7 +3527,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>94</v>
       </c>
@@ -3553,7 +3550,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>94</v>
       </c>
@@ -3576,7 +3573,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>94</v>
       </c>
@@ -3590,7 +3587,7 @@
         <v>339</v>
       </c>
       <c r="E76" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F76" t="s">
         <v>416</v>
@@ -3599,7 +3596,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>94</v>
       </c>
@@ -3622,7 +3619,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>94</v>
       </c>
@@ -3645,7 +3642,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>94</v>
       </c>
@@ -3668,7 +3665,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>94</v>
       </c>
@@ -3691,7 +3688,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>94</v>
       </c>
@@ -3705,7 +3702,7 @@
         <v>329</v>
       </c>
       <c r="E81" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F81" t="s">
         <v>405</v>
@@ -3714,7 +3711,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>94</v>
       </c>
@@ -3737,7 +3734,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>94</v>
       </c>
@@ -3751,7 +3748,7 @@
         <v>294</v>
       </c>
       <c r="E83" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="F83" t="s">
         <v>428</v>
@@ -3760,7 +3757,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>94</v>
       </c>
@@ -3783,7 +3780,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>94</v>
       </c>
@@ -3806,7 +3803,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>94</v>
       </c>
@@ -3829,7 +3826,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>94</v>
       </c>
@@ -3843,7 +3840,7 @@
         <v>301</v>
       </c>
       <c r="E87" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F87" t="s">
         <v>402</v>
@@ -3852,7 +3849,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>94</v>
       </c>
@@ -3869,13 +3866,13 @@
         <v>366</v>
       </c>
       <c r="F88" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="G88" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>94</v>
       </c>
@@ -3898,7 +3895,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>94</v>
       </c>
@@ -3921,7 +3918,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>94</v>
       </c>
@@ -3938,13 +3935,13 @@
         <v>347</v>
       </c>
       <c r="F91" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G91" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>94</v>
       </c>
@@ -3967,7 +3964,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>94</v>
       </c>
@@ -3990,7 +3987,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>94</v>
       </c>
@@ -4013,7 +4010,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>94</v>
       </c>
@@ -4036,7 +4033,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>94</v>
       </c>
@@ -4059,7 +4056,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>94</v>
       </c>
@@ -4082,7 +4079,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>94</v>
       </c>
@@ -4105,7 +4102,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>94</v>
       </c>
@@ -4119,7 +4116,7 @@
         <v>335</v>
       </c>
       <c r="E99" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F99" t="s">
         <v>416</v>
@@ -4128,7 +4125,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>94</v>
       </c>
@@ -4151,7 +4148,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>94</v>
       </c>
@@ -4174,7 +4171,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>94</v>
       </c>
@@ -4197,7 +4194,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>94</v>
       </c>
@@ -4220,7 +4217,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>94</v>
       </c>
@@ -4243,7 +4240,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>94</v>
       </c>
@@ -4257,7 +4254,7 @@
         <v>294</v>
       </c>
       <c r="E105" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F105" t="s">
         <v>355</v>
@@ -4266,7 +4263,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>94</v>
       </c>
@@ -4289,7 +4286,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>94</v>
       </c>
@@ -4312,7 +4309,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>94</v>
       </c>
@@ -4326,7 +4323,7 @@
         <v>325</v>
       </c>
       <c r="E108" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F108" t="s">
         <v>439</v>
@@ -4335,7 +4332,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>94</v>
       </c>
@@ -4358,7 +4355,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>94</v>
       </c>
@@ -4381,7 +4378,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>94</v>
       </c>
@@ -4404,7 +4401,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>94</v>
       </c>
@@ -4427,7 +4424,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>94</v>
       </c>
@@ -4450,7 +4447,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>94</v>
       </c>
@@ -4473,7 +4470,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>94</v>
       </c>
@@ -4496,7 +4493,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>94</v>
       </c>
@@ -4519,7 +4516,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>94</v>
       </c>
@@ -4542,7 +4539,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>94</v>
       </c>
@@ -4565,7 +4562,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>94</v>
       </c>
@@ -4588,7 +4585,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>94</v>
       </c>
@@ -4602,7 +4599,7 @@
         <v>319</v>
       </c>
       <c r="E120" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F120" t="s">
         <v>404</v>
@@ -4611,7 +4608,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>94</v>
       </c>
@@ -4634,7 +4631,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>94</v>
       </c>
@@ -4657,7 +4654,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>94</v>
       </c>
@@ -4671,7 +4668,7 @@
         <v>454</v>
       </c>
       <c r="E123" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F123" t="s">
         <v>416</v>
@@ -4680,7 +4677,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>94</v>
       </c>
@@ -4703,7 +4700,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>94</v>
       </c>
@@ -4726,7 +4723,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>94</v>
       </c>
@@ -4749,7 +4746,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>94</v>
       </c>
@@ -4772,7 +4769,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>94</v>
       </c>
@@ -4786,7 +4783,7 @@
         <v>217</v>
       </c>
       <c r="E128" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F128" t="s">
         <v>387</v>
@@ -4795,7 +4792,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>94</v>
       </c>
@@ -4818,7 +4815,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>94</v>
       </c>
@@ -4841,7 +4838,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>94</v>
       </c>
@@ -4864,7 +4861,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>94</v>
       </c>
@@ -4887,7 +4884,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>94</v>
       </c>
@@ -4910,7 +4907,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>94</v>
       </c>
@@ -4933,7 +4930,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>94</v>
       </c>
@@ -4950,13 +4947,13 @@
         <v>386</v>
       </c>
       <c r="F135" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="G135" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>94</v>
       </c>
@@ -4979,7 +4976,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>94</v>
       </c>
@@ -4993,7 +4990,7 @@
         <v>315</v>
       </c>
       <c r="E137" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F137" t="s">
         <v>446</v>
@@ -5002,7 +4999,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>94</v>
       </c>
@@ -5025,7 +5022,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>94</v>
       </c>
@@ -5048,7 +5045,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>94</v>
       </c>
@@ -5065,13 +5062,13 @@
         <v>370</v>
       </c>
       <c r="F140" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="G140" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>94</v>
       </c>
@@ -5094,7 +5091,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>94</v>
       </c>
@@ -5117,7 +5114,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>94</v>
       </c>
@@ -5140,7 +5137,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>94</v>
       </c>
@@ -5163,7 +5160,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>94</v>
       </c>
@@ -5186,7 +5183,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>94</v>
       </c>
@@ -5200,7 +5197,7 @@
         <v>217</v>
       </c>
       <c r="E146" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F146" t="s">
         <v>422</v>
@@ -5209,7 +5206,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>94</v>
       </c>
@@ -5232,7 +5229,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>94</v>
       </c>
@@ -5255,7 +5252,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>94</v>
       </c>
@@ -5272,13 +5269,13 @@
         <v>351</v>
       </c>
       <c r="F149" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G149" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>94</v>
       </c>
@@ -5301,7 +5298,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>94</v>
       </c>
@@ -5324,7 +5321,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>94</v>
       </c>
@@ -5347,7 +5344,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>94</v>
       </c>
@@ -5370,7 +5367,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>94</v>
       </c>
@@ -5393,7 +5390,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>94</v>
       </c>
@@ -5416,7 +5413,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>94</v>
       </c>
@@ -5439,7 +5436,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>94</v>
       </c>
@@ -5462,7 +5459,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>94</v>
       </c>
@@ -5485,7 +5482,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>94</v>
       </c>
@@ -5508,7 +5505,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>94</v>
       </c>
@@ -5531,7 +5528,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>94</v>
       </c>
@@ -5554,7 +5551,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>94</v>
       </c>
@@ -5577,7 +5574,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>94</v>
       </c>
@@ -5600,7 +5597,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>94</v>
       </c>
@@ -5623,7 +5620,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>94</v>
       </c>
@@ -5646,7 +5643,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>94</v>
       </c>
@@ -5669,7 +5666,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>94</v>
       </c>
@@ -5683,7 +5680,7 @@
         <v>297</v>
       </c>
       <c r="E167" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F167" t="s">
         <v>403</v>
@@ -5692,7 +5689,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>94</v>
       </c>
@@ -5715,7 +5712,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>94</v>
       </c>
@@ -5738,7 +5735,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>94</v>
       </c>
@@ -5761,7 +5758,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>94</v>
       </c>
@@ -5778,13 +5775,13 @@
         <v>416</v>
       </c>
       <c r="F171" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="G171" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>94</v>
       </c>
@@ -5807,7 +5804,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>94</v>
       </c>
@@ -5830,7 +5827,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>94</v>
       </c>
@@ -5853,91 +5850,91 @@
         <v>292</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C176" s="1"/>
     </row>
-    <row r="201" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="201" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C201" s="2"/>
     </row>
-    <row r="202" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="202" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C202" s="2"/>
     </row>
-    <row r="203" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="203" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C203" s="2"/>
     </row>
-    <row r="204" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="204" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C204" s="2"/>
     </row>
-    <row r="205" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="205" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C205" s="2"/>
     </row>
-    <row r="206" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="206" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C206" s="2"/>
     </row>
-    <row r="207" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="207" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C207" s="2"/>
     </row>
-    <row r="208" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="208" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C208" s="2"/>
     </row>
-    <row r="209" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="209" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C209" s="2"/>
     </row>
-    <row r="210" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="210" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C210" s="2"/>
     </row>
-    <row r="211" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="211" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C211" s="2"/>
     </row>
-    <row r="212" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="212" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C212" s="2"/>
     </row>
-    <row r="213" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="213" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C213" s="2"/>
     </row>
-    <row r="214" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="214" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C214" s="2"/>
     </row>
-    <row r="215" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="215" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C215" s="2"/>
     </row>
-    <row r="216" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="216" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C216" s="2"/>
     </row>
-    <row r="217" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="217" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C217" s="2"/>
     </row>
-    <row r="218" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="218" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C218" s="2"/>
     </row>
-    <row r="219" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="219" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C219" s="2"/>
     </row>
-    <row r="220" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="220" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C220" s="2"/>
     </row>
-    <row r="221" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="221" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C221" s="2"/>
     </row>
-    <row r="222" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="222" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C222" s="2"/>
     </row>
-    <row r="223" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="223" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C223" s="2"/>
     </row>
-    <row r="224" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="224" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C224" s="2"/>
     </row>
-    <row r="225" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="225" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C225" s="2"/>
     </row>
-    <row r="226" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="226" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C226" s="2"/>
     </row>
-    <row r="227" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="227" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C227" s="2"/>
     </row>
-    <row r="229" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="229" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C229" s="2"/>
     </row>
   </sheetData>

--- a/data/EN/games_config/toxic_games_5_USA.xlsx
+++ b/data/EN/games_config/toxic_games_5_USA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vfionda/Library/CloudStorage/GoogleDrive-valeria.fionda@unical.it/My Drive/didattica/Tesi/2025/Artigas Herold/Cards_Against_AI/data/EN/games_config/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\!Master\Tesis\3 Codigo\Cards_Against_AI\data\EN\games_config\games\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41B36B83-87F9-0B40-8A58-E6BEA4E27AD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE90771E-6C4D-45CA-8F9E-F1DBA775D23E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="23260" windowHeight="12460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet_1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="478">
   <si>
     <t>black_id</t>
   </si>
@@ -1419,6 +1419,9 @@
   </si>
   <si>
     <t>W204</t>
+  </si>
+  <si>
+    <t>w213</t>
   </si>
   <si>
     <t>W123</t>
@@ -1482,7 +1485,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1834,18 +1836,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J229"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="11.6640625" customWidth="1"/>
     <col min="4" max="4" width="10.33203125" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" customWidth="1"/>
-    <col min="6" max="6" width="10.5" customWidth="1"/>
-    <col min="7" max="7" width="10.83203125" customWidth="1"/>
-    <col min="8" max="9" width="11.1640625" customWidth="1"/>
-    <col min="10" max="10" width="11.5" customWidth="1"/>
+    <col min="5" max="5" width="11.77734375" customWidth="1"/>
+    <col min="6" max="6" width="10.5546875" customWidth="1"/>
+    <col min="7" max="7" width="10.88671875" customWidth="1"/>
+    <col min="8" max="8" width="11.109375" customWidth="1"/>
+    <col min="9" max="9" width="11.21875" customWidth="1"/>
+    <col min="10" max="10" width="11.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>93</v>
       </c>
@@ -1871,7 +1874,7 @@
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>94</v>
       </c>
@@ -1894,7 +1897,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>94</v>
       </c>
@@ -1917,7 +1920,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>94</v>
       </c>
@@ -1940,7 +1943,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>94</v>
       </c>
@@ -1963,7 +1966,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>94</v>
       </c>
@@ -1986,7 +1989,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>94</v>
       </c>
@@ -2009,7 +2012,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>94</v>
       </c>
@@ -2032,7 +2035,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>94</v>
       </c>
@@ -2055,7 +2058,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>94</v>
       </c>
@@ -2078,7 +2081,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>94</v>
       </c>
@@ -2101,7 +2104,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>94</v>
       </c>
@@ -2124,7 +2127,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>94</v>
       </c>
@@ -2147,7 +2150,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>94</v>
       </c>
@@ -2170,7 +2173,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>94</v>
       </c>
@@ -2193,7 +2196,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>94</v>
       </c>
@@ -2216,7 +2219,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>94</v>
       </c>
@@ -2239,7 +2242,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>94</v>
       </c>
@@ -2262,7 +2265,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>94</v>
       </c>
@@ -2285,7 +2288,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>94</v>
       </c>
@@ -2308,7 +2311,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>94</v>
       </c>
@@ -2331,7 +2334,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>94</v>
       </c>
@@ -2354,7 +2357,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>94</v>
       </c>
@@ -2377,7 +2380,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>94</v>
       </c>
@@ -2400,7 +2403,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>94</v>
       </c>
@@ -2423,7 +2426,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>94</v>
       </c>
@@ -2446,7 +2449,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>94</v>
       </c>
@@ -2469,7 +2472,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>94</v>
       </c>
@@ -2492,7 +2495,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>94</v>
       </c>
@@ -2515,7 +2518,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>94</v>
       </c>
@@ -2538,7 +2541,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>94</v>
       </c>
@@ -2561,7 +2564,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>94</v>
       </c>
@@ -2584,7 +2587,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>94</v>
       </c>
@@ -2607,7 +2610,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>94</v>
       </c>
@@ -2630,7 +2633,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>94</v>
       </c>
@@ -2653,7 +2656,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>94</v>
       </c>
@@ -2676,7 +2679,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>94</v>
       </c>
@@ -2699,7 +2702,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>94</v>
       </c>
@@ -2722,7 +2725,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>94</v>
       </c>
@@ -2745,7 +2748,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>94</v>
       </c>
@@ -2768,7 +2771,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>94</v>
       </c>
@@ -2791,7 +2794,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>94</v>
       </c>
@@ -2814,7 +2817,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>94</v>
       </c>
@@ -2837,7 +2840,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>94</v>
       </c>
@@ -2860,7 +2863,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>94</v>
       </c>
@@ -2883,7 +2886,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>94</v>
       </c>
@@ -2906,7 +2909,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>94</v>
       </c>
@@ -2929,7 +2932,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>94</v>
       </c>
@@ -2952,7 +2955,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>94</v>
       </c>
@@ -2975,7 +2978,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>94</v>
       </c>
@@ -2998,7 +3001,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>94</v>
       </c>
@@ -3021,7 +3024,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>94</v>
       </c>
@@ -3044,7 +3047,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>94</v>
       </c>
@@ -3067,7 +3070,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>94</v>
       </c>
@@ -3090,7 +3093,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>94</v>
       </c>
@@ -3113,7 +3116,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>94</v>
       </c>
@@ -3136,7 +3139,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>94</v>
       </c>
@@ -3159,7 +3162,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>94</v>
       </c>
@@ -3182,7 +3185,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>94</v>
       </c>
@@ -3205,7 +3208,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>94</v>
       </c>
@@ -3228,7 +3231,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>94</v>
       </c>
@@ -3251,7 +3254,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>94</v>
       </c>
@@ -3274,7 +3277,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>94</v>
       </c>
@@ -3297,7 +3300,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>94</v>
       </c>
@@ -3320,7 +3323,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>94</v>
       </c>
@@ -3343,7 +3346,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>94</v>
       </c>
@@ -3366,7 +3369,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>94</v>
       </c>
@@ -3389,7 +3392,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>94</v>
       </c>
@@ -3403,7 +3406,7 @@
         <v>330</v>
       </c>
       <c r="E68" t="s">
-        <v>427</v>
+        <v>462</v>
       </c>
       <c r="F68" t="s">
         <v>403</v>
@@ -3412,7 +3415,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>94</v>
       </c>
@@ -3435,7 +3438,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>94</v>
       </c>
@@ -3458,7 +3461,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>94</v>
       </c>
@@ -3475,13 +3478,13 @@
         <v>381</v>
       </c>
       <c r="F71" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="G71" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>94</v>
       </c>
@@ -3495,7 +3498,7 @@
         <v>303</v>
       </c>
       <c r="E72" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F72" t="s">
         <v>426</v>
@@ -3504,7 +3507,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>94</v>
       </c>
@@ -3527,7 +3530,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>94</v>
       </c>
@@ -3550,7 +3553,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>94</v>
       </c>
@@ -3573,7 +3576,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>94</v>
       </c>
@@ -3587,7 +3590,7 @@
         <v>339</v>
       </c>
       <c r="E76" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F76" t="s">
         <v>416</v>
@@ -3596,7 +3599,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>94</v>
       </c>
@@ -3619,7 +3622,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>94</v>
       </c>
@@ -3642,7 +3645,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>94</v>
       </c>
@@ -3665,7 +3668,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>94</v>
       </c>
@@ -3688,7 +3691,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>94</v>
       </c>
@@ -3702,7 +3705,7 @@
         <v>329</v>
       </c>
       <c r="E81" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F81" t="s">
         <v>405</v>
@@ -3711,7 +3714,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>94</v>
       </c>
@@ -3734,7 +3737,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>94</v>
       </c>
@@ -3748,7 +3751,7 @@
         <v>294</v>
       </c>
       <c r="E83" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F83" t="s">
         <v>428</v>
@@ -3757,7 +3760,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>94</v>
       </c>
@@ -3780,7 +3783,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>94</v>
       </c>
@@ -3803,7 +3806,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>94</v>
       </c>
@@ -3826,7 +3829,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>94</v>
       </c>
@@ -3840,7 +3843,7 @@
         <v>301</v>
       </c>
       <c r="E87" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F87" t="s">
         <v>402</v>
@@ -3849,7 +3852,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>94</v>
       </c>
@@ -3866,13 +3869,13 @@
         <v>366</v>
       </c>
       <c r="F88" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G88" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>94</v>
       </c>
@@ -3895,7 +3898,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>94</v>
       </c>
@@ -3918,7 +3921,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="91" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>94</v>
       </c>
@@ -3935,13 +3938,13 @@
         <v>347</v>
       </c>
       <c r="F91" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G91" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>94</v>
       </c>
@@ -3964,7 +3967,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>94</v>
       </c>
@@ -3987,7 +3990,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>94</v>
       </c>
@@ -4010,7 +4013,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="95" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>94</v>
       </c>
@@ -4033,7 +4036,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>94</v>
       </c>
@@ -4056,7 +4059,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>94</v>
       </c>
@@ -4079,7 +4082,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>94</v>
       </c>
@@ -4102,7 +4105,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="99" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>94</v>
       </c>
@@ -4116,7 +4119,7 @@
         <v>335</v>
       </c>
       <c r="E99" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F99" t="s">
         <v>416</v>
@@ -4125,7 +4128,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="100" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>94</v>
       </c>
@@ -4148,7 +4151,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>94</v>
       </c>
@@ -4171,7 +4174,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>94</v>
       </c>
@@ -4194,7 +4197,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="103" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>94</v>
       </c>
@@ -4217,7 +4220,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>94</v>
       </c>
@@ -4240,7 +4243,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>94</v>
       </c>
@@ -4254,7 +4257,7 @@
         <v>294</v>
       </c>
       <c r="E105" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F105" t="s">
         <v>355</v>
@@ -4263,7 +4266,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>94</v>
       </c>
@@ -4286,7 +4289,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="107" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>94</v>
       </c>
@@ -4309,7 +4312,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>94</v>
       </c>
@@ -4323,7 +4326,7 @@
         <v>325</v>
       </c>
       <c r="E108" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F108" t="s">
         <v>439</v>
@@ -4332,7 +4335,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>94</v>
       </c>
@@ -4355,7 +4358,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>94</v>
       </c>
@@ -4378,7 +4381,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="111" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>94</v>
       </c>
@@ -4401,7 +4404,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>94</v>
       </c>
@@ -4424,7 +4427,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="113" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>94</v>
       </c>
@@ -4447,7 +4450,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="114" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>94</v>
       </c>
@@ -4470,7 +4473,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>94</v>
       </c>
@@ -4493,7 +4496,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="116" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>94</v>
       </c>
@@ -4516,7 +4519,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>94</v>
       </c>
@@ -4539,7 +4542,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>94</v>
       </c>
@@ -4562,7 +4565,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>94</v>
       </c>
@@ -4585,7 +4588,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>94</v>
       </c>
@@ -4599,7 +4602,7 @@
         <v>319</v>
       </c>
       <c r="E120" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F120" t="s">
         <v>404</v>
@@ -4608,7 +4611,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="121" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>94</v>
       </c>
@@ -4631,7 +4634,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="122" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>94</v>
       </c>
@@ -4654,7 +4657,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>94</v>
       </c>
@@ -4668,7 +4671,7 @@
         <v>454</v>
       </c>
       <c r="E123" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F123" t="s">
         <v>416</v>
@@ -4677,7 +4680,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="124" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>94</v>
       </c>
@@ -4700,7 +4703,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="125" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>94</v>
       </c>
@@ -4723,7 +4726,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="126" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>94</v>
       </c>
@@ -4746,7 +4749,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="127" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>94</v>
       </c>
@@ -4769,7 +4772,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="128" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>94</v>
       </c>
@@ -4783,7 +4786,7 @@
         <v>217</v>
       </c>
       <c r="E128" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F128" t="s">
         <v>387</v>
@@ -4792,7 +4795,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>94</v>
       </c>
@@ -4815,7 +4818,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>94</v>
       </c>
@@ -4838,7 +4841,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="131" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>94</v>
       </c>
@@ -4861,7 +4864,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>94</v>
       </c>
@@ -4884,7 +4887,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>94</v>
       </c>
@@ -4907,7 +4910,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>94</v>
       </c>
@@ -4930,7 +4933,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="135" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>94</v>
       </c>
@@ -4947,13 +4950,13 @@
         <v>386</v>
       </c>
       <c r="F135" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="G135" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="136" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>94</v>
       </c>
@@ -4976,7 +4979,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="137" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>94</v>
       </c>
@@ -4990,7 +4993,7 @@
         <v>315</v>
       </c>
       <c r="E137" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F137" t="s">
         <v>446</v>
@@ -4999,7 +5002,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>94</v>
       </c>
@@ -5022,7 +5025,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>94</v>
       </c>
@@ -5045,7 +5048,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>94</v>
       </c>
@@ -5062,13 +5065,13 @@
         <v>370</v>
       </c>
       <c r="F140" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="G140" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>94</v>
       </c>
@@ -5091,7 +5094,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>94</v>
       </c>
@@ -5114,7 +5117,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>94</v>
       </c>
@@ -5137,7 +5140,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>94</v>
       </c>
@@ -5160,7 +5163,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>94</v>
       </c>
@@ -5183,7 +5186,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>94</v>
       </c>
@@ -5197,7 +5200,7 @@
         <v>217</v>
       </c>
       <c r="E146" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F146" t="s">
         <v>422</v>
@@ -5206,7 +5209,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>94</v>
       </c>
@@ -5229,7 +5232,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>94</v>
       </c>
@@ -5252,7 +5255,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>94</v>
       </c>
@@ -5269,13 +5272,13 @@
         <v>351</v>
       </c>
       <c r="F149" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="G149" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>94</v>
       </c>
@@ -5298,7 +5301,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>94</v>
       </c>
@@ -5321,7 +5324,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>94</v>
       </c>
@@ -5344,7 +5347,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>94</v>
       </c>
@@ -5367,7 +5370,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>94</v>
       </c>
@@ -5390,7 +5393,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>94</v>
       </c>
@@ -5413,7 +5416,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>94</v>
       </c>
@@ -5436,7 +5439,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>94</v>
       </c>
@@ -5459,7 +5462,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>94</v>
       </c>
@@ -5482,7 +5485,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>94</v>
       </c>
@@ -5505,7 +5508,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>94</v>
       </c>
@@ -5528,7 +5531,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>94</v>
       </c>
@@ -5551,7 +5554,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>94</v>
       </c>
@@ -5574,7 +5577,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>94</v>
       </c>
@@ -5597,7 +5600,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>94</v>
       </c>
@@ -5620,7 +5623,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>94</v>
       </c>
@@ -5643,7 +5646,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>94</v>
       </c>
@@ -5666,7 +5669,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>94</v>
       </c>
@@ -5680,7 +5683,7 @@
         <v>297</v>
       </c>
       <c r="E167" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F167" t="s">
         <v>403</v>
@@ -5689,7 +5692,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>94</v>
       </c>
@@ -5712,7 +5715,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>94</v>
       </c>
@@ -5735,7 +5738,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>94</v>
       </c>
@@ -5758,7 +5761,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>94</v>
       </c>
@@ -5775,13 +5778,13 @@
         <v>416</v>
       </c>
       <c r="F171" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="G171" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>94</v>
       </c>
@@ -5804,7 +5807,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>94</v>
       </c>
@@ -5827,7 +5830,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>94</v>
       </c>
@@ -5850,91 +5853,91 @@
         <v>292</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C176" s="1"/>
     </row>
-    <row r="201" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="201" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C201" s="2"/>
     </row>
-    <row r="202" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="202" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C202" s="2"/>
     </row>
-    <row r="203" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="203" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C203" s="2"/>
     </row>
-    <row r="204" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="204" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C204" s="2"/>
     </row>
-    <row r="205" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="205" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C205" s="2"/>
     </row>
-    <row r="206" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="206" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C206" s="2"/>
     </row>
-    <row r="207" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="207" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C207" s="2"/>
     </row>
-    <row r="208" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="208" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C208" s="2"/>
     </row>
-    <row r="209" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="209" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C209" s="2"/>
     </row>
-    <row r="210" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="210" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C210" s="2"/>
     </row>
-    <row r="211" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="211" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C211" s="2"/>
     </row>
-    <row r="212" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="212" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C212" s="2"/>
     </row>
-    <row r="213" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="213" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C213" s="2"/>
     </row>
-    <row r="214" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="214" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C214" s="2"/>
     </row>
-    <row r="215" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="215" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C215" s="2"/>
     </row>
-    <row r="216" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="216" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C216" s="2"/>
     </row>
-    <row r="217" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="217" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C217" s="2"/>
     </row>
-    <row r="218" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="218" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C218" s="2"/>
     </row>
-    <row r="219" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="219" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C219" s="2"/>
     </row>
-    <row r="220" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="220" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C220" s="2"/>
     </row>
-    <row r="221" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="221" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C221" s="2"/>
     </row>
-    <row r="222" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="222" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C222" s="2"/>
     </row>
-    <row r="223" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="223" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C223" s="2"/>
     </row>
-    <row r="224" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="224" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C224" s="2"/>
     </row>
-    <row r="225" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="225" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C225" s="2"/>
     </row>
-    <row r="226" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="226" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C226" s="2"/>
     </row>
-    <row r="227" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="227" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C227" s="2"/>
     </row>
-    <row r="229" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="229" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C229" s="2"/>
     </row>
   </sheetData>
